--- a/src/lib/__fixtures__/portfolio-import.xlsx
+++ b/src/lib/__fixtures__/portfolio-import.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -443,6 +443,9 @@
       <c r="M1" t="str">
         <v>contact_email</v>
       </c>
+      <c r="N1">
+        <v>2019</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -467,7 +470,7 @@
         <v>safe</v>
       </c>
       <c r="H2" s="2">
-        <v>44634.99947916667</v>
+        <v>44635</v>
       </c>
       <c r="I2" t="str">
         <v>current</v>
@@ -487,7 +490,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N2"/>
   </ignoredErrors>
 </worksheet>
 </file>